--- a/Indeed_Candidate_Database.xlsx
+++ b/Indeed_Candidate_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection workbookPassword="CAA7" lockStructure="1"/>
+  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access &amp; Handling" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Candidates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Applications" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Access &amp; Handling" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Candidates'!$A$1:$T$16</definedName>
@@ -524,7 +524,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30-Oct-2026 by recruiter1. CONFIDENTIAL - authorised recruitment team only.</t>
+          <t>Generated 30-Oct-2026 by saini. CONFIDENTIAL - authorised recruitment team only.</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="CAA7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2176,7 +2175,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="CAA7"/>
   <autoFilter ref="A1:T16"/>
   <dataValidations count="2">
     <dataValidation sqref="O2:O16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -2873,7 +2871,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="CAA7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2900,7 +2897,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Authorised users: hr.lead,recruiter1</t>
+          <t>Authorised users: (not set - sample data only)</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2951,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="CAA7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>